--- a/public/data/Master App Timesheet.xlsx
+++ b/public/data/Master App Timesheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\timesheet-app\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50140550-7E97-49E1-B568-C6F9000A0E59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F2CDAA7-1FB6-49B9-A870-21EE58EC147E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="10060" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vendor Entry Sheet" sheetId="5" r:id="rId1"/>
@@ -22,6 +22,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Vendor Entry Sheet'!$A$3:$K$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Work Orders'!$A$1:$F$397</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Vendor Entry Sheet'!$A$1:$J$50</definedName>
     <definedName name="SMS">Names!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -7089,7 +7090,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="70" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="89" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">

--- a/public/data/Master App Timesheet.xlsx
+++ b/public/data/Master App Timesheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\timesheet-app\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F2CDAA7-1FB6-49B9-A870-21EE58EC147E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D26E902-3FCA-4E9C-8725-E8819756D339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10" yWindow="10" windowWidth="19180" windowHeight="10060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vendor Entry Sheet" sheetId="5" r:id="rId1"/>
@@ -2961,6 +2961,123 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>57855</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>21166</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>275165</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>183443</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14DD9482-4B03-D611-85AE-5009589DAE86}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="10800000" flipV="1">
+          <a:off x="3042355" y="7422444"/>
+          <a:ext cx="4937477" cy="2363610"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-AU" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" sz="1100" b="1"/>
+            <a:t>Greatland Supervisor Name:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-AU" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-AU" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" sz="1100" b="1"/>
+            <a:t>Signiture</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-AU" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-AU" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-AU" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" sz="1100" b="1"/>
+            <a:t>Contractor Supervisor Name:</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-AU" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="en-AU" sz="1100"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-AU" sz="1100" b="1"/>
+            <a:t>Signiture</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>228599</xdr:colOff>
       <xdr:row>1</xdr:row>
@@ -7091,6 +7208,7 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="89" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
@@ -30257,15 +30375,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="a1bbf4fc-2070-4842-8cf2-c42346818ea9" xsi:nil="true"/>
@@ -30274,6 +30383,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -30520,20 +30638,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71C3BF75-E265-495B-A1EF-9F0F8014FF62}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C286B8F-44DD-46A1-8664-5B3AFC40D364}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="a1bbf4fc-2070-4842-8cf2-c42346818ea9"/>
     <ds:schemaRef ds:uri="d41b7399-51ed-4fce-9e89-79a41c55ed41"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71C3BF75-E265-495B-A1EF-9F0F8014FF62}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/public/data/Master App Timesheet.xlsx
+++ b/public/data/Master App Timesheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\timesheet-app\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D26E902-3FCA-4E9C-8725-E8819756D339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4502BF4E-C8AA-4BBE-8DAB-86832BAB6AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vendor Entry Sheet" sheetId="5" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2366" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2371" uniqueCount="650">
   <si>
     <t xml:space="preserve">Date
 </t>
@@ -2042,6 +2042,12 @@
   </si>
   <si>
     <t>272SUSS</t>
+  </si>
+  <si>
+    <t>Jackshaft Inspection</t>
+  </si>
+  <si>
+    <t>TMS Emergent</t>
   </si>
 </sst>
 </file>
@@ -29644,11 +29650,22 @@
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A304" s="5"/>
+      <c r="A304" s="5" t="s">
+        <v>151</v>
+      </c>
       <c r="B304" s="5"/>
-      <c r="C304" s="5"/>
-      <c r="D304" s="5"/>
-      <c r="E304" s="5"/>
+      <c r="C304" s="5" t="s">
+        <v>648</v>
+      </c>
+      <c r="D304" s="5" t="s">
+        <v>649</v>
+      </c>
+      <c r="E304" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="F304" s="5" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A305" s="5"/>
@@ -30375,6 +30392,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="a1bbf4fc-2070-4842-8cf2-c42346818ea9" xsi:nil="true"/>
@@ -30383,15 +30409,6 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -30638,20 +30655,20 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71C3BF75-E265-495B-A1EF-9F0F8014FF62}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C286B8F-44DD-46A1-8664-5B3AFC40D364}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="a1bbf4fc-2070-4842-8cf2-c42346818ea9"/>
     <ds:schemaRef ds:uri="d41b7399-51ed-4fce-9e89-79a41c55ed41"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{71C3BF75-E265-495B-A1EF-9F0F8014FF62}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/public/data/Master App Timesheet.xlsx
+++ b/public/data/Master App Timesheet.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\timesheet-app\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51658F14-B69A-4609-ABE5-453EA350F1A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39594FFC-2497-4234-B0AC-78F6277F6937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vendor Entry Sheet" sheetId="5" r:id="rId1"/>
     <sheet name="Bulk Upload Tool (NML USE ONLY)" sheetId="1" r:id="rId2"/>
-    <sheet name="Approval Box (OFFICE ONLY)" sheetId="6" r:id="rId3"/>
-    <sheet name="Names" sheetId="7" r:id="rId4"/>
+    <sheet name="Names" sheetId="7" r:id="rId3"/>
+    <sheet name="Approval Box (OFFICE ONLY)" sheetId="6" r:id="rId4"/>
     <sheet name="Work Orders" sheetId="8" r:id="rId5"/>
   </sheets>
   <definedNames>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1280" uniqueCount="347">
   <si>
     <t xml:space="preserve">Date
 </t>
@@ -281,9 +281,6 @@
   </si>
   <si>
     <t>Work Order Header</t>
-  </si>
-  <si>
-    <t>Boom</t>
   </si>
   <si>
     <t>Company</t>
@@ -21385,19 +21382,6 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr>
-    <tabColor rgb="FF00B050"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A173344C-5E6C-4937-A6DB-D67A680918AA}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -21422,7 +21406,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="52" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B1" s="52" t="s">
         <v>40</v>
@@ -21444,7 +21428,7 @@
         <v>42</v>
       </c>
       <c r="J1" s="52" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K1" s="54" t="s">
         <v>43</v>
@@ -21456,10 +21440,10 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B2" s="55" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C2" s="56">
         <v>90303035</v>
@@ -21470,11 +21454,11 @@
       <c r="E2" s="21"/>
       <c r="F2"/>
       <c r="G2" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H2" s="57"/>
       <c r="J2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K2" s="21">
         <v>4700022986</v>
@@ -21486,25 +21470,25 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B3" s="55" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C3" s="56">
         <v>90301394</v>
       </c>
       <c r="D3" s="46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E3" s="21"/>
       <c r="F3"/>
       <c r="G3" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H3" s="57"/>
       <c r="J3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K3" s="21">
         <v>4700022697</v>
@@ -21516,25 +21500,25 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C4" s="56">
         <v>90303036</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E4" s="21"/>
       <c r="F4"/>
       <c r="G4" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H4" s="57"/>
       <c r="J4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K4" s="21">
         <v>4700022696</v>
@@ -21546,25 +21530,25 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5" s="55" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C5" s="56">
         <v>90302810</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E5" s="21"/>
       <c r="F5"/>
       <c r="G5" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H5" s="57"/>
       <c r="J5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K5" s="21">
         <v>4700022985</v>
@@ -21576,21 +21560,21 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B6" s="55" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C6" s="56">
         <v>90302811</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E6" s="21"/>
       <c r="F6"/>
       <c r="G6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H6" s="57"/>
       <c r="K6"/>
@@ -21598,21 +21582,21 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B7" s="55" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C7" s="56">
         <v>90301575</v>
       </c>
       <c r="D7" s="46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E7" s="21"/>
       <c r="F7"/>
       <c r="G7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="H7" s="57"/>
       <c r="K7" s="57"/>
@@ -21620,21 +21604,21 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B8" s="55" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C8" s="56">
         <v>90302899</v>
       </c>
       <c r="D8" s="46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E8" s="21"/>
       <c r="F8"/>
       <c r="G8" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="H8" s="57"/>
       <c r="K8" s="57"/>
@@ -21642,10 +21626,10 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B9" s="55" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C9" s="56">
         <v>90303047</v>
@@ -21656,7 +21640,7 @@
       <c r="E9" s="21"/>
       <c r="F9"/>
       <c r="G9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H9" s="57"/>
       <c r="K9" s="57"/>
@@ -21664,21 +21648,21 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B10" s="55" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C10" s="56">
         <v>90302812</v>
       </c>
       <c r="D10" s="46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E10" s="21"/>
       <c r="F10"/>
       <c r="G10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H10" s="57"/>
       <c r="K10" s="57"/>
@@ -21686,21 +21670,21 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B11" s="55" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C11" s="56">
         <v>90303037</v>
       </c>
       <c r="D11" s="46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E11" s="21"/>
       <c r="F11"/>
       <c r="G11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H11" s="57"/>
       <c r="K11"/>
@@ -21708,17 +21692,17 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" s="55"/>
       <c r="C12" s="56"/>
       <c r="D12" s="46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E12" s="21"/>
       <c r="F12"/>
       <c r="G12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H12" s="57"/>
       <c r="K12"/>
@@ -21726,21 +21710,21 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C13" s="56">
         <v>90303038</v>
       </c>
       <c r="D13" s="46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E13" s="21"/>
       <c r="F13"/>
       <c r="G13" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H13" s="57"/>
       <c r="K13"/>
@@ -21748,21 +21732,21 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B14" s="55" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C14" s="56">
         <v>90300883</v>
       </c>
       <c r="D14" s="46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E14" s="21"/>
       <c r="F14"/>
       <c r="G14" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H14" s="57"/>
       <c r="K14"/>
@@ -21770,21 +21754,21 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B15" s="55" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C15" s="56">
         <v>90303039</v>
       </c>
       <c r="D15" s="46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E15" s="21"/>
       <c r="F15"/>
       <c r="G15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="H15" s="57"/>
       <c r="K15"/>
@@ -21792,21 +21776,21 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B16" s="55" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C16" s="56">
         <v>90301596</v>
       </c>
       <c r="D16" s="46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E16" s="21"/>
       <c r="F16"/>
       <c r="G16" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H16" s="57"/>
       <c r="K16"/>
@@ -21814,21 +21798,21 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B17" s="55" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C17" s="56">
         <v>90302084</v>
       </c>
       <c r="D17" s="46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E17" s="21"/>
       <c r="F17"/>
       <c r="G17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H17" s="57"/>
       <c r="K17"/>
@@ -21836,21 +21820,21 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B18" s="55" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C18" s="56">
         <v>90303040</v>
       </c>
       <c r="D18" s="46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E18" s="21"/>
       <c r="F18"/>
       <c r="G18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H18" s="57"/>
       <c r="K18"/>
@@ -21858,21 +21842,21 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B19" s="55" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C19" s="56">
         <v>90302814</v>
       </c>
       <c r="D19" s="46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E19" s="21"/>
       <c r="F19"/>
       <c r="G19" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H19" s="57"/>
       <c r="K19"/>
@@ -21880,21 +21864,21 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B20" s="55" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C20" s="56">
         <v>90303041</v>
       </c>
       <c r="D20" s="46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E20" s="21"/>
       <c r="F20"/>
       <c r="G20" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H20" s="57"/>
       <c r="K20"/>
@@ -21902,16 +21886,16 @@
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B21" s="55" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C21" s="56">
         <v>90303042</v>
       </c>
       <c r="D21" s="46" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E21" s="21"/>
       <c r="F21"/>
@@ -21922,16 +21906,16 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B22" s="55" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C22" s="56">
         <v>90301904</v>
       </c>
       <c r="D22" s="46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E22" s="21"/>
       <c r="F22"/>
@@ -21942,16 +21926,16 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B23" s="55" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C23" s="56">
         <v>90303043</v>
       </c>
       <c r="D23" s="46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E23" s="21"/>
       <c r="F23"/>
@@ -21962,16 +21946,16 @@
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B24" s="55" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C24" s="56">
         <v>90300831</v>
       </c>
       <c r="D24" s="46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E24" s="21"/>
       <c r="F24"/>
@@ -21982,16 +21966,16 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B25" s="46" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C25" s="56">
         <v>90303044</v>
       </c>
       <c r="D25" s="46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E25" s="21"/>
       <c r="F25"/>
@@ -22002,16 +21986,16 @@
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B26" s="55" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C26" s="56">
         <v>90302816</v>
       </c>
       <c r="D26" s="46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E26" s="21"/>
       <c r="F26"/>
@@ -22022,16 +22006,16 @@
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B27" s="55" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C27" s="56">
         <v>90300877</v>
       </c>
       <c r="D27" s="46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E27" s="21"/>
       <c r="F27"/>
@@ -22042,16 +22026,16 @@
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B28" s="55" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C28" s="56">
         <v>90303045</v>
       </c>
       <c r="D28" s="46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E28" s="21"/>
       <c r="F28"/>
@@ -22062,16 +22046,16 @@
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" s="46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B29" s="55" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C29" s="56">
         <v>90300744</v>
       </c>
       <c r="D29" s="46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E29" s="21"/>
       <c r="F29"/>
@@ -22082,10 +22066,10 @@
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B30" s="46" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C30" s="56">
         <v>90302878</v>
@@ -22102,16 +22086,16 @@
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B31" s="46" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C31" s="56">
         <v>90302879</v>
       </c>
       <c r="D31" s="46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E31" s="21"/>
       <c r="F31"/>
@@ -22122,16 +22106,16 @@
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B32" s="46" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C32" s="56">
         <v>90302565</v>
       </c>
       <c r="D32" s="46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E32" s="21"/>
       <c r="F32"/>
@@ -22142,16 +22126,16 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B33" s="46" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C33" s="56">
         <v>90302880</v>
       </c>
       <c r="D33" s="46" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E33" s="21"/>
       <c r="F33"/>
@@ -22162,16 +22146,16 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B34" s="46" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C34" s="56">
         <v>90301205</v>
       </c>
       <c r="D34" s="46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E34" s="21"/>
       <c r="F34"/>
@@ -22182,16 +22166,16 @@
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B35" s="46" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C35" s="56">
         <v>90302881</v>
       </c>
       <c r="D35" s="46" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E35" s="21"/>
       <c r="F35"/>
@@ -22202,10 +22186,10 @@
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B36" s="46" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C36" s="56">
         <v>90302882</v>
@@ -22222,16 +22206,16 @@
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B37" s="55" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C37" s="56">
         <v>90303049</v>
       </c>
       <c r="D37" s="46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E37" s="21"/>
       <c r="F37"/>
@@ -22242,16 +22226,16 @@
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B38" s="46" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C38" s="56">
         <v>90302884</v>
       </c>
       <c r="D38" s="46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E38" s="21"/>
       <c r="F38"/>
@@ -22262,16 +22246,16 @@
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B39" s="46" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C39" s="56">
         <v>90302885</v>
       </c>
       <c r="D39" s="46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E39" s="21"/>
       <c r="F39"/>
@@ -22282,16 +22266,16 @@
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B40" s="46" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C40" s="56">
         <v>90302886</v>
       </c>
       <c r="D40" s="46" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E40" s="21"/>
       <c r="F40"/>
@@ -22302,16 +22286,16 @@
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B41" s="46" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C41" s="56">
         <v>90302887</v>
       </c>
       <c r="D41" s="46" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E41" s="21"/>
       <c r="F41"/>
@@ -22322,7 +22306,7 @@
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C42"/>
       <c r="D42" s="46" t="s">
@@ -22337,16 +22321,16 @@
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B43" s="55" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C43" s="56">
         <v>90302823</v>
       </c>
       <c r="D43" s="46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E43" s="21"/>
       <c r="F43"/>
@@ -22357,16 +22341,16 @@
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B44" s="55" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C44" s="56">
         <v>90302824</v>
       </c>
       <c r="D44" s="46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E44" s="21"/>
       <c r="F44"/>
@@ -22377,16 +22361,16 @@
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B45" s="55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C45" s="56">
         <v>90302825</v>
       </c>
       <c r="D45" s="58" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E45" s="21"/>
       <c r="F45"/>
@@ -22397,10 +22381,10 @@
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B46" s="59" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C46" s="56">
         <v>90300463</v>
@@ -22417,16 +22401,16 @@
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B47" s="46" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C47" s="60">
         <v>90302435</v>
       </c>
       <c r="D47" s="46" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E47" s="21"/>
       <c r="F47"/>
@@ -22437,16 +22421,16 @@
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B48" s="55" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C48" s="56">
         <v>90302890</v>
       </c>
       <c r="D48" s="46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E48" s="21"/>
       <c r="F48"/>
@@ -22457,16 +22441,16 @@
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" s="46" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B49" s="55" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C49" s="56">
         <v>90302891</v>
       </c>
       <c r="D49" s="58" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E49" s="21"/>
       <c r="F49"/>
@@ -22477,10 +22461,10 @@
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A50" s="46" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="B50" s="46" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C50" s="56">
         <v>90140920</v>
@@ -22497,16 +22481,16 @@
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A51" s="46" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="B51" s="46" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C51" s="56">
         <v>90300209</v>
       </c>
       <c r="D51" s="46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E51" s="21"/>
       <c r="F51"/>
@@ -22517,16 +22501,16 @@
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A52" s="46" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="B52" s="46" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C52" s="60">
         <v>90302877</v>
       </c>
       <c r="D52" s="46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E52" s="21"/>
       <c r="F52"/>
@@ -22537,16 +22521,16 @@
     </row>
     <row r="53" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A53" s="46" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="B53" s="55" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C53" s="60">
         <v>90302964</v>
       </c>
       <c r="D53" s="46" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E53" s="21"/>
       <c r="F53"/>
@@ -22557,16 +22541,16 @@
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A54" s="46" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="B54" s="46" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C54" s="60">
         <v>90302465</v>
       </c>
       <c r="D54" s="46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E54" s="21"/>
       <c r="F54"/>
@@ -22577,16 +22561,16 @@
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A55" s="46" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="B55" s="46" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C55" s="56">
         <v>90302706</v>
       </c>
       <c r="D55" s="46" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E55" s="21"/>
       <c r="F55"/>
@@ -22597,16 +22581,16 @@
     </row>
     <row r="56" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A56" s="46" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="B56" s="46" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C56" s="56">
         <v>90302755</v>
       </c>
       <c r="D56" s="46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E56" s="21"/>
       <c r="F56"/>
@@ -22617,16 +22601,16 @@
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A57" s="46" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="B57" s="46" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C57" s="60">
         <v>90301259</v>
       </c>
       <c r="D57" s="46" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E57" s="21"/>
       <c r="F57"/>
@@ -22637,16 +22621,16 @@
     </row>
     <row r="58" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A58" s="46" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="B58" s="46" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C58" s="56">
         <v>90302707</v>
       </c>
       <c r="D58" s="46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E58" s="21"/>
       <c r="F58"/>
@@ -22657,16 +22641,16 @@
     </row>
     <row r="59" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A59" s="46" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="B59" s="46" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C59" s="56">
         <v>90302329</v>
       </c>
       <c r="D59" s="46" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E59" s="21"/>
       <c r="F59"/>
@@ -22677,16 +22661,16 @@
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A60" s="46" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="B60" s="46" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C60" s="56">
         <v>90300214</v>
       </c>
       <c r="D60" s="46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E60" s="21"/>
       <c r="F60"/>
@@ -22697,10 +22681,10 @@
     </row>
     <row r="61" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A61" s="46" t="s">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="B61" s="46" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C61" s="56">
         <v>90112330</v>
@@ -22717,10 +22701,10 @@
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A62" s="46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B62" s="46" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C62" s="56">
         <v>90128099</v>
@@ -22737,16 +22721,16 @@
     </row>
     <row r="63" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A63" s="46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B63" s="46" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C63" s="56">
         <v>90302036</v>
       </c>
       <c r="D63" s="46" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E63" s="21"/>
       <c r="F63"/>
@@ -22757,16 +22741,16 @@
     </row>
     <row r="64" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A64" s="46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B64" s="46" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C64" s="56">
         <v>90302520</v>
       </c>
       <c r="D64" s="46" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E64" s="21"/>
       <c r="F64"/>
@@ -22777,16 +22761,16 @@
     </row>
     <row r="65" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A65" s="46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B65" s="46" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C65" s="56">
         <v>90302598</v>
       </c>
       <c r="D65" s="46" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E65" s="21"/>
       <c r="F65"/>
@@ -22797,16 +22781,16 @@
     </row>
     <row r="66" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A66" s="46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B66" s="46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C66" s="56">
         <v>90302416</v>
       </c>
       <c r="D66" s="46" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E66" s="21"/>
       <c r="F66"/>
@@ -22817,16 +22801,16 @@
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A67" s="46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B67" s="46" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C67" s="56">
         <v>90301293</v>
       </c>
       <c r="D67" s="46" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E67" s="21"/>
       <c r="F67"/>
@@ -22837,16 +22821,16 @@
     </row>
     <row r="68" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A68" s="46" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B68" s="46" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C68" s="56">
         <v>90302753</v>
       </c>
       <c r="D68" s="46" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E68" s="21"/>
       <c r="F68"/>
@@ -22857,10 +22841,10 @@
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A69" s="46" t="s">
+        <v>91</v>
+      </c>
+      <c r="B69" s="46" t="s">
         <v>92</v>
-      </c>
-      <c r="B69" s="46" t="s">
-        <v>93</v>
       </c>
       <c r="C69" s="56">
         <v>90128100</v>
@@ -23004,6 +22988,19 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -23033,2213 +23030,2213 @@
         <v>48</v>
       </c>
       <c r="D1" s="48" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E1" s="48" t="s">
         <v>46</v>
       </c>
       <c r="F1" s="48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>194</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>195</v>
-      </c>
       <c r="F2" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="D3" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>194</v>
-      </c>
       <c r="E3" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F3" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>193</v>
-      </c>
       <c r="D4" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F4" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="5" t="s">
+      <c r="D5" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>199</v>
-      </c>
       <c r="E5" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F5" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>202</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F6" s="61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>201</v>
-      </c>
       <c r="D7" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F7" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>201</v>
-      </c>
       <c r="D8" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F8" s="61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>201</v>
-      </c>
       <c r="D9" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F9" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>201</v>
-      </c>
       <c r="D10" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F10" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>201</v>
-      </c>
       <c r="D11" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F11" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="5" t="s">
+      <c r="D12" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>210</v>
-      </c>
       <c r="E12" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F12" s="61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>213</v>
-      </c>
       <c r="E13" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F13" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>212</v>
       </c>
-      <c r="D14" s="5" t="s">
-        <v>213</v>
-      </c>
       <c r="E14" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F14" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>212</v>
-      </c>
       <c r="D15" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F15" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>217</v>
-      </c>
       <c r="E16" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F16" s="61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>220</v>
-      </c>
       <c r="E17" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F17" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>219</v>
-      </c>
       <c r="D18" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F18" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>219</v>
-      </c>
       <c r="D19" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F19" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>219</v>
-      </c>
       <c r="D20" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F20" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" s="5" t="s">
+      <c r="D21" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>227</v>
-      </c>
       <c r="F21" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>225</v>
-      </c>
       <c r="D22" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F22" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>225</v>
-      </c>
       <c r="D23" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F23" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>225</v>
-      </c>
       <c r="D24" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F24" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="5" t="s">
+      <c r="D25" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F25" s="61" t="s">
         <v>233</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="F25" s="61" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C26" s="5" t="s">
+      <c r="D26" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="D26" s="5" t="s">
-        <v>237</v>
-      </c>
       <c r="E26" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F26" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>236</v>
-      </c>
       <c r="D27" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F27" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>236</v>
-      </c>
       <c r="D28" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F28" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>236</v>
-      </c>
       <c r="D29" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F29" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>236</v>
-      </c>
       <c r="D30" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F30" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>244</v>
-      </c>
       <c r="E31" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F31" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32" s="5" t="s">
+      <c r="D32" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="D32" s="5" t="s">
-        <v>247</v>
-      </c>
       <c r="E32" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F32" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>246</v>
-      </c>
       <c r="D33" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F33" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>246</v>
-      </c>
       <c r="D34" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F34" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>251</v>
-      </c>
       <c r="D35" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F35" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>251</v>
-      </c>
       <c r="D36" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F36" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="B37" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>251</v>
-      </c>
       <c r="D37" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F37" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C38" s="5" t="s">
-        <v>251</v>
-      </c>
       <c r="D38" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F38" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>251</v>
-      </c>
       <c r="D39" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F39" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C40" s="5" t="s">
+      <c r="D40" s="5" t="s">
         <v>253</v>
       </c>
-      <c r="D40" s="5" t="s">
-        <v>254</v>
-      </c>
       <c r="E40" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F40" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>253</v>
-      </c>
       <c r="D41" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F41" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C42" s="5" t="s">
-        <v>253</v>
-      </c>
       <c r="D42" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F42" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C43" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B43" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C43" s="5" t="s">
-        <v>253</v>
-      </c>
       <c r="D43" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F43" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C44" s="5" t="s">
-        <v>253</v>
-      </c>
       <c r="D44" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="E44" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="E44" s="5" t="s">
-        <v>258</v>
-      </c>
       <c r="F44" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B45" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C45" s="5" t="s">
-        <v>253</v>
-      </c>
       <c r="D45" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F45" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C46" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C46" s="5" t="s">
-        <v>253</v>
-      </c>
       <c r="D46" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F46" s="61" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C47" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>253</v>
-      </c>
       <c r="D47" s="5" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F47" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C48" s="5" t="s">
-        <v>253</v>
-      </c>
       <c r="D48" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F48" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B49" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C49" s="5" t="s">
-        <v>253</v>
-      </c>
       <c r="D49" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F49" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C50" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="C50" s="5" t="s">
-        <v>253</v>
-      </c>
       <c r="D50" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F50" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C51" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B51" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C51" s="5" t="s">
-        <v>253</v>
-      </c>
       <c r="D51" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F51" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C52" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>253</v>
-      </c>
       <c r="D52" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F52" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C53" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B53" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C53" s="5" t="s">
-        <v>253</v>
-      </c>
       <c r="D53" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F53" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C54" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B54" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C54" s="5" t="s">
-        <v>253</v>
-      </c>
       <c r="D54" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F54" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B55" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>253</v>
-      </c>
       <c r="D55" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F55" s="61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C56" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B56" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C56" s="5" t="s">
-        <v>253</v>
-      </c>
       <c r="D56" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F56" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C57" s="5" t="s">
         <v>252</v>
       </c>
-      <c r="B57" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C57" s="5" t="s">
-        <v>253</v>
-      </c>
       <c r="D57" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F57" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C58" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="B58" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C58" s="5" t="s">
+      <c r="D58" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="D58" s="5" t="s">
-        <v>273</v>
-      </c>
       <c r="E58" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F58" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C59" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="B59" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C59" s="5" t="s">
-        <v>272</v>
-      </c>
       <c r="D59" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F59" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C60" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="B60" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>272</v>
-      </c>
       <c r="D60" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F60" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C61" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="B61" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C61" s="5" t="s">
-        <v>272</v>
-      </c>
       <c r="D61" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F61" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C62" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="B62" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>272</v>
-      </c>
       <c r="D62" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F62" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C63" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="B63" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C63" s="5" t="s">
-        <v>272</v>
-      </c>
       <c r="D63" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F63" s="61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="C64" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="D64" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="C64" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="D64" s="5" t="s">
-        <v>280</v>
-      </c>
       <c r="E64" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F64" s="61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C65" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B65" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C65" s="5" t="s">
+      <c r="D65" s="5" t="s">
         <v>282</v>
       </c>
-      <c r="D65" s="5" t="s">
+      <c r="E65" s="5" t="s">
         <v>283</v>
       </c>
-      <c r="E65" s="5" t="s">
-        <v>284</v>
-      </c>
       <c r="F65" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C66" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B66" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>282</v>
-      </c>
       <c r="D66" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F66" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C67" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B67" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>282</v>
-      </c>
       <c r="D67" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="E67" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="E67" s="5" t="s">
-        <v>287</v>
-      </c>
       <c r="F67" s="61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C68" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B68" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C68" s="5" t="s">
-        <v>282</v>
-      </c>
       <c r="D68" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F68" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C69" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B69" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C69" s="5" t="s">
-        <v>282</v>
-      </c>
       <c r="D69" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="E69" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="E69" s="5" t="s">
-        <v>290</v>
-      </c>
       <c r="F69" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C70" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="B70" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C70" s="5" t="s">
+      <c r="D70" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="D70" s="5" t="s">
-        <v>293</v>
-      </c>
       <c r="E70" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F70" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C71" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="B71" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>292</v>
-      </c>
       <c r="D71" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="E71" s="5" t="s">
         <v>294</v>
       </c>
-      <c r="E71" s="5" t="s">
-        <v>295</v>
-      </c>
       <c r="F71" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C72" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="B72" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>292</v>
-      </c>
       <c r="D72" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F72" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C73" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="B73" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>292</v>
-      </c>
       <c r="D73" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F73" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="C74" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="D74" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="C74" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="D74" s="5" t="s">
-        <v>299</v>
-      </c>
       <c r="E74" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F74" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C75" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="B75" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C75" s="5" t="s">
-        <v>292</v>
-      </c>
       <c r="D75" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F75" s="61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C76" s="5" t="s">
         <v>291</v>
       </c>
-      <c r="B76" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>292</v>
-      </c>
       <c r="D76" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F76" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C77" s="5" t="s">
         <v>302</v>
       </c>
-      <c r="B77" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>303</v>
-      </c>
       <c r="D77" s="5" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F77" s="61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C78" s="5" t="s">
         <v>304</v>
       </c>
-      <c r="B78" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>305</v>
-      </c>
       <c r="D78" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F78" s="61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C79" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="B79" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C79" s="5" t="s">
-        <v>307</v>
-      </c>
       <c r="D79" s="5" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F79" s="61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C80" s="5" t="s">
         <v>308</v>
       </c>
-      <c r="B80" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>309</v>
-      </c>
       <c r="D80" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F80" s="61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C81" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="B81" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C81" s="5" t="s">
-        <v>311</v>
-      </c>
       <c r="D81" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F81" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C82" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="B82" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C82" s="5" t="s">
+      <c r="D82" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="D82" s="5" t="s">
-        <v>314</v>
-      </c>
       <c r="E82" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F82" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C83" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="B83" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C83" s="5" t="s">
-        <v>313</v>
-      </c>
       <c r="D83" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F83" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C84" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="B84" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>313</v>
-      </c>
       <c r="D84" s="5" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F84" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C85" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B85" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C85" s="5" t="s">
+      <c r="D85" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="D85" s="5" t="s">
-        <v>319</v>
-      </c>
       <c r="E85" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F85" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C86" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B86" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C86" s="5" t="s">
-        <v>318</v>
-      </c>
       <c r="D86" s="5" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F86" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C87" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B87" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C87" s="5" t="s">
-        <v>318</v>
-      </c>
       <c r="D87" s="5" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F87" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C88" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B88" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>318</v>
-      </c>
       <c r="D88" s="5" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F88" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C89" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B89" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>318</v>
-      </c>
       <c r="D89" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F89" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="C90" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="D90" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="C90" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>325</v>
-      </c>
       <c r="E90" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F90" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C91" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B91" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C91" s="5" t="s">
-        <v>318</v>
-      </c>
       <c r="D91" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F91" s="61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C92" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B92" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C92" s="5" t="s">
-        <v>318</v>
-      </c>
       <c r="D92" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F92" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C93" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B93" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>318</v>
-      </c>
       <c r="D93" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F93" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C94" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B94" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>318</v>
-      </c>
       <c r="D94" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F94" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C95" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B95" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>318</v>
-      </c>
       <c r="D95" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F95" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C96" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B96" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="C96" s="5" t="s">
-        <v>318</v>
-      </c>
       <c r="D96" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F96" s="61" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C97" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B97" s="5" t="s">
+      <c r="D97" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="C97" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="D97" s="5" t="s">
-        <v>330</v>
-      </c>
       <c r="E97" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F97" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C98" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B98" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>318</v>
-      </c>
       <c r="D98" s="5" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F98" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C99" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B99" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>318</v>
-      </c>
       <c r="D99" s="5" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F99" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C100" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B100" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>318</v>
-      </c>
       <c r="D100" s="5" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F100" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C101" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B101" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>318</v>
-      </c>
       <c r="D101" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F101" s="61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C102" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B102" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C102" s="5" t="s">
-        <v>318</v>
-      </c>
       <c r="D102" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F102" s="61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="C103" s="5" t="s">
         <v>317</v>
       </c>
-      <c r="B103" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C103" s="5" t="s">
-        <v>318</v>
-      </c>
       <c r="D103" s="5" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F103" s="61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C104" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="B104" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C104" s="5" t="s">
+      <c r="D104" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="D104" s="5" t="s">
-        <v>338</v>
-      </c>
       <c r="E104" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F104" s="61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C105" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="B105" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>337</v>
-      </c>
       <c r="D105" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F105" s="61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C106" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="B106" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>337</v>
-      </c>
       <c r="D106" s="5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F106" s="61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A107" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C107" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="B107" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>337</v>
-      </c>
       <c r="D107" s="5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F107" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C108" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="B108" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>337</v>
-      </c>
       <c r="D108" s="5" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F108" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C109" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="B109" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C109" s="5" t="s">
+      <c r="D109" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="D109" s="5" t="s">
-        <v>345</v>
-      </c>
       <c r="E109" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F109" s="61" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C110" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="B110" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C110" s="5" t="s">
-        <v>344</v>
-      </c>
       <c r="D110" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F110" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="17" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C111" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="B111" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>344</v>
-      </c>
       <c r="D111" s="5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F111" s="61" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.35">
